--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T2_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="73">
   <si>
     <t/>
   </si>
@@ -57,78 +57,81 @@
     <t>N</t>
   </si>
   <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (1) </t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Mean/(SE)</t>
+  </si>
+  <si>
+    <t>1.225</t>
+  </si>
+  <si>
+    <t>(0.209)</t>
+  </si>
+  <si>
+    <t>7.058</t>
+  </si>
+  <si>
+    <t>(0.898)</t>
+  </si>
+  <si>
+    <t>1.999</t>
+  </si>
+  <si>
+    <t>(0.609)</t>
+  </si>
+  <si>
+    <t>5.553</t>
+  </si>
+  <si>
+    <t>(0.782)</t>
+  </si>
+  <si>
+    <t>1.716</t>
+  </si>
+  <si>
+    <t>(0.201)</t>
+  </si>
+  <si>
+    <t>12.019</t>
+  </si>
+  <si>
+    <t>(1.566)</t>
+  </si>
+  <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t>(0.000)</t>
+  </si>
+  <si>
+    <t>0.614</t>
+  </si>
+  <si>
+    <t>(0.127)</t>
+  </si>
+  <si>
+    <t>8.057</t>
+  </si>
+  <si>
+    <t>(0.925)</t>
+  </si>
+  <si>
+    <t>3.252</t>
+  </si>
+  <si>
+    <t>(1.071)</t>
+  </si>
+  <si>
     <t>58</t>
   </si>
   <si>
-    <t xml:space="preserve"> (1) </t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Mean/(SE)</t>
-  </si>
-  <si>
-    <t>1.098</t>
-  </si>
-  <si>
-    <t>(0.194)</t>
-  </si>
-  <si>
-    <t>6.328</t>
-  </si>
-  <si>
-    <t>(0.854)</t>
-  </si>
-  <si>
-    <t>3.043</t>
-  </si>
-  <si>
-    <t>(0.853)</t>
-  </si>
-  <si>
-    <t>6.369</t>
-  </si>
-  <si>
-    <t>(0.902)</t>
-  </si>
-  <si>
-    <t>1.608</t>
-  </si>
-  <si>
-    <t>(0.196)</t>
-  </si>
-  <si>
-    <t>10.914</t>
-  </si>
-  <si>
-    <t>(1.473)</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>(0.000)</t>
-  </si>
-  <si>
-    <t>0.620</t>
-  </si>
-  <si>
-    <t>(0.130)</t>
-  </si>
-  <si>
-    <t>7.400</t>
-  </si>
-  <si>
-    <t>(0.882)</t>
-  </si>
-  <si>
-    <t>5.619</t>
-  </si>
-  <si>
-    <t>(1.684)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> (2) </t>
   </si>
   <si>
@@ -189,7 +192,7 @@
     <t>(0.663)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>.n</t>
@@ -204,31 +207,31 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.323</t>
-  </si>
-  <si>
-    <t>2.345*</t>
-  </si>
-  <si>
-    <t>0.595</t>
-  </si>
-  <si>
-    <t>0.569</t>
-  </si>
-  <si>
-    <t>-0.012</t>
-  </si>
-  <si>
-    <t>-0.345</t>
-  </si>
-  <si>
-    <t>-0.337**</t>
-  </si>
-  <si>
-    <t>2.761*</t>
-  </si>
-  <si>
-    <t>-1.589</t>
+    <t>0.196</t>
+  </si>
+  <si>
+    <t>1.615</t>
+  </si>
+  <si>
+    <t>1.639*</t>
+  </si>
+  <si>
+    <t>1.385</t>
+  </si>
+  <si>
+    <t>-0.120</t>
+  </si>
+  <si>
+    <t>-1.450</t>
+  </si>
+  <si>
+    <t>-0.330**</t>
+  </si>
+  <si>
+    <t>2.104</t>
+  </si>
+  <si>
+    <t>0.778</t>
   </si>
 </sst>
 </file>
@@ -289,13 +292,13 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
@@ -312,13 +315,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -341,7 +344,7 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -355,16 +358,16 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -381,7 +384,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -401,16 +404,16 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -427,7 +430,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -447,16 +450,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -473,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -493,16 +496,16 @@
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
@@ -519,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -539,16 +542,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -565,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -585,16 +588,16 @@
         <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -611,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
@@ -631,16 +634,16 @@
         <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -677,16 +680,16 @@
         <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
@@ -703,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -723,16 +726,16 @@
         <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -769,16 +772,16 @@
         <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -795,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>
